--- a/reportes/ventas.xlsx
+++ b/reportes/ventas.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,22 +424,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-15 18:25:39</v>
+        <v>2026-06-03 07:08:25</v>
       </c>
       <c r="C2" t="str">
-        <v>achinti</v>
+        <v>Administrador</v>
       </c>
       <c r="D2" t="str">
-        <v>achinti</v>
+        <v>ACHINTI</v>
       </c>
       <c r="E2">
-        <v>35000</v>
+        <v>200000</v>
       </c>
       <c r="F2">
-        <v>80000</v>
+        <v>50000</v>
       </c>
       <c r="G2" t="str">
         <v>entregado</v>
@@ -447,22 +447,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-14 18:52:24</v>
+        <v>2026-06-03 07:01:09</v>
       </c>
       <c r="C3" t="str">
+        <v>Administrador</v>
+      </c>
+      <c r="D3" t="str">
         <v>achinti</v>
       </c>
-      <c r="D3" t="str">
-        <v>Sin cliente</v>
-      </c>
       <c r="E3">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="F3">
-        <v>60000</v>
+        <v>110000</v>
       </c>
       <c r="G3" t="str">
         <v>entregado</v>
@@ -470,22 +470,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-14 18:20:26</v>
+        <v>2026-06-03 07:00:04</v>
       </c>
       <c r="C4" t="str">
-        <v>achinti</v>
+        <v>Administrador</v>
       </c>
       <c r="D4" t="str">
-        <v>achinti</v>
+        <v>Sin cliente</v>
       </c>
       <c r="E4">
-        <v>60000</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>55000</v>
+        <v>110000</v>
       </c>
       <c r="G4" t="str">
         <v>entregado</v>
@@ -493,13 +493,13 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-05-14 18:19:26</v>
+        <v>2026-05-20 22:38:49</v>
       </c>
       <c r="C5" t="str">
-        <v>achinti</v>
+        <v>Administrador</v>
       </c>
       <c r="D5" t="str">
         <v>Sin cliente</v>
@@ -508,291 +508,15 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>65000</v>
+        <v>130000</v>
       </c>
       <c r="G5" t="str">
-        <v>entregado</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>12</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-05-10 15:53:21</v>
-      </c>
-      <c r="C6" t="str">
-        <v>achinti</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Sin cliente</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>1700000</v>
-      </c>
-      <c r="G6" t="str">
-        <v>entregado</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>11</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-05-10 15:52:45</v>
-      </c>
-      <c r="C7" t="str">
-        <v>achinti</v>
-      </c>
-      <c r="D7" t="str">
-        <v>cesar</v>
-      </c>
-      <c r="E7">
-        <v>50000</v>
-      </c>
-      <c r="F7">
-        <v>100000</v>
-      </c>
-      <c r="G7" t="str">
-        <v>entregado</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>10</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-05-10 15:50:43</v>
-      </c>
-      <c r="C8" t="str">
-        <v>achinti</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Sin cliente</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>100000</v>
-      </c>
-      <c r="G8" t="str">
-        <v>entregado</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>9</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-05-08 17:12:43</v>
-      </c>
-      <c r="C9" t="str">
-        <v>achinti</v>
-      </c>
-      <c r="D9" t="str">
-        <v>pepito</v>
-      </c>
-      <c r="E9">
-        <v>50000</v>
-      </c>
-      <c r="F9">
-        <v>50000</v>
-      </c>
-      <c r="G9" t="str">
-        <v>entregado</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-05-08 07:40:03</v>
-      </c>
-      <c r="C10" t="str">
-        <v>achinti</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Sin cliente</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>220000</v>
-      </c>
-      <c r="G10" t="str">
-        <v>entregado</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>7</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-05-07 14:36:32</v>
-      </c>
-      <c r="C11" t="str">
-        <v>achinti</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Sin cliente</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>650000</v>
-      </c>
-      <c r="G11" t="str">
-        <v>entregado</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12">
-        <v>6</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-05-07 14:28:47</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Administrador</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Sin cliente</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>700000</v>
-      </c>
-      <c r="G12" t="str">
-        <v>entregado</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13">
-        <v>5</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-05-07 14:26:18</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Administrador</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Sin cliente</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>170000</v>
-      </c>
-      <c r="G13" t="str">
-        <v>entregado</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14">
-        <v>4</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-05-07 14:20:22</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Administrador</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Sin cliente</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>120000</v>
-      </c>
-      <c r="G14" t="str">
-        <v>entregado</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15">
-        <v>3</v>
-      </c>
-      <c r="B15" t="str">
-        <v>2026-05-07 08:41:11</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Administrador</v>
-      </c>
-      <c r="D15" t="str">
-        <v>achinti</v>
-      </c>
-      <c r="E15">
-        <v>50000</v>
-      </c>
-      <c r="F15">
-        <v>190000</v>
-      </c>
-      <c r="G15" t="str">
-        <v>entregado</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <v>2</v>
-      </c>
-      <c r="B16" t="str">
-        <v>2026-05-07 07:15:43</v>
-      </c>
-      <c r="C16" t="str">
-        <v>achinti</v>
-      </c>
-      <c r="D16" t="str">
-        <v>Sin cliente</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>1900000</v>
-      </c>
-      <c r="G16" t="str">
-        <v>entregado</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17">
-        <v>1</v>
-      </c>
-      <c r="B17" t="str">
-        <v>2026-05-07 07:14:40</v>
-      </c>
-      <c r="C17" t="str">
-        <v>achinti</v>
-      </c>
-      <c r="D17" t="str">
-        <v>Ariadna Bashir Cañon Ramirez</v>
-      </c>
-      <c r="E17">
-        <v>100000</v>
-      </c>
-      <c r="F17">
-        <v>120000</v>
-      </c>
-      <c r="G17" t="str">
         <v>entregado</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reportes/ventas.xlsx
+++ b/reportes/ventas.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,10 +424,10 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-12 06:36:20</v>
+        <v>2026-06-13 20:18:04</v>
       </c>
       <c r="C2" t="str">
         <v>Administrador</v>
@@ -439,7 +439,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>76000</v>
+        <v>65000</v>
       </c>
       <c r="G2" t="str">
         <v>entregado</v>
@@ -447,10 +447,10 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-06-12 06:31:22</v>
+        <v>2026-06-12 06:36:20</v>
       </c>
       <c r="C3" t="str">
         <v>Administrador</v>
@@ -470,10 +470,10 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-06-11 21:07:36</v>
+        <v>2026-06-12 06:31:22</v>
       </c>
       <c r="C4" t="str">
         <v>Administrador</v>
@@ -485,7 +485,7 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>170000</v>
+        <v>76000</v>
       </c>
       <c r="G4" t="str">
         <v>entregado</v>
@@ -493,13 +493,13 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-06-11 17:30:45</v>
+        <v>2026-06-11 21:07:36</v>
       </c>
       <c r="C5" t="str">
-        <v>achinti morales hernández</v>
+        <v>Administrador</v>
       </c>
       <c r="D5" t="str">
         <v>Sin cliente</v>
@@ -508,7 +508,7 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>455000</v>
+        <v>170000</v>
       </c>
       <c r="G5" t="str">
         <v>entregado</v>
@@ -516,10 +516,10 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-06-11 17:29:29</v>
+        <v>2026-06-11 17:30:45</v>
       </c>
       <c r="C6" t="str">
         <v>achinti morales hernández</v>
@@ -531,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>55000</v>
+        <v>455000</v>
       </c>
       <c r="G6" t="str">
         <v>entregado</v>
@@ -539,10 +539,10 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-06-11 17:07:24</v>
+        <v>2026-06-11 17:29:29</v>
       </c>
       <c r="C7" t="str">
         <v>achinti morales hernández</v>
@@ -562,10 +562,10 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-06-11 16:55:29</v>
+        <v>2026-06-11 17:07:24</v>
       </c>
       <c r="C8" t="str">
         <v>achinti morales hernández</v>
@@ -585,10 +585,10 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-06-11 16:48:17</v>
+        <v>2026-06-11 16:55:29</v>
       </c>
       <c r="C9" t="str">
         <v>achinti morales hernández</v>
@@ -608,10 +608,10 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-06-11 16:41:14</v>
+        <v>2026-06-11 16:48:17</v>
       </c>
       <c r="C10" t="str">
         <v>achinti morales hernández</v>
@@ -631,10 +631,10 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-06-11 16:38:26</v>
+        <v>2026-06-11 16:41:14</v>
       </c>
       <c r="C11" t="str">
         <v>achinti morales hernández</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-06-11 16:37:14</v>
+        <v>2026-06-11 16:38:26</v>
       </c>
       <c r="C12" t="str">
         <v>achinti morales hernández</v>
@@ -677,10 +677,10 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-06-11 16:34:41</v>
+        <v>2026-06-11 16:37:14</v>
       </c>
       <c r="C13" t="str">
         <v>achinti morales hernández</v>
@@ -700,10 +700,10 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-06-11 16:32:51</v>
+        <v>2026-06-11 16:34:41</v>
       </c>
       <c r="C14" t="str">
         <v>achinti morales hernández</v>
@@ -723,10 +723,10 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-06-11 16:32:47</v>
+        <v>2026-06-11 16:32:51</v>
       </c>
       <c r="C15" t="str">
         <v>achinti morales hernández</v>
@@ -746,10 +746,10 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-06-11 09:19:13</v>
+        <v>2026-06-11 16:32:47</v>
       </c>
       <c r="C16" t="str">
         <v>achinti morales hernández</v>
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>120000</v>
+        <v>55000</v>
       </c>
       <c r="G16" t="str">
         <v>entregado</v>
@@ -769,10 +769,10 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-06-11 09:18:49</v>
+        <v>2026-06-11 09:19:13</v>
       </c>
       <c r="C17" t="str">
         <v>achinti morales hernández</v>
@@ -792,10 +792,10 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-06-11 09:18:25</v>
+        <v>2026-06-11 09:18:49</v>
       </c>
       <c r="C18" t="str">
         <v>achinti morales hernández</v>
@@ -807,7 +807,7 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>720000</v>
+        <v>120000</v>
       </c>
       <c r="G18" t="str">
         <v>entregado</v>
@@ -815,10 +815,10 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-06-11 09:18:02</v>
+        <v>2026-06-11 09:18:25</v>
       </c>
       <c r="C19" t="str">
         <v>achinti morales hernández</v>
@@ -830,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>4800000</v>
+        <v>720000</v>
       </c>
       <c r="G19" t="str">
         <v>entregado</v>
@@ -838,10 +838,10 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-06-11 09:16:29</v>
+        <v>2026-06-11 09:18:02</v>
       </c>
       <c r="C20" t="str">
         <v>achinti morales hernández</v>
@@ -853,7 +853,7 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>560000</v>
+        <v>4800000</v>
       </c>
       <c r="G20" t="str">
         <v>entregado</v>
@@ -861,10 +861,10 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B21" t="str">
-        <v>2026-06-11 09:12:56</v>
+        <v>2026-06-11 09:16:29</v>
       </c>
       <c r="C21" t="str">
         <v>achinti morales hernández</v>
@@ -876,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>120000</v>
+        <v>560000</v>
       </c>
       <c r="G21" t="str">
         <v>entregado</v>
@@ -884,13 +884,13 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B22" t="str">
-        <v>2026-06-11 09:10:01</v>
+        <v>2026-06-11 09:12:56</v>
       </c>
       <c r="C22" t="str">
-        <v>Administrador</v>
+        <v>achinti morales hernández</v>
       </c>
       <c r="D22" t="str">
         <v>Sin cliente</v>
@@ -899,7 +899,7 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>105000</v>
+        <v>120000</v>
       </c>
       <c r="G22" t="str">
         <v>entregado</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B23" t="str">
-        <v>2026-06-11 09:08:21</v>
+        <v>2026-06-11 09:10:01</v>
       </c>
       <c r="C23" t="str">
         <v>Administrador</v>
@@ -930,10 +930,10 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B24" t="str">
-        <v>2026-06-11 07:36:14</v>
+        <v>2026-06-11 09:08:21</v>
       </c>
       <c r="C24" t="str">
         <v>Administrador</v>
@@ -953,10 +953,10 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B25" t="str">
-        <v>2026-06-11 07:16:23</v>
+        <v>2026-06-11 07:36:14</v>
       </c>
       <c r="C25" t="str">
         <v>Administrador</v>
@@ -974,9 +974,32 @@
         <v>entregado</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26">
+        <v>1</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2026-06-11 07:16:23</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Administrador</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Sin cliente</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>105000</v>
+      </c>
+      <c r="G26" t="str">
+        <v>entregado</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G26"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reportes/ventas.xlsx
+++ b/reportes/ventas.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G33"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,13 +424,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-13 20:18:04</v>
+        <v>2026-06-16 20:39:32</v>
       </c>
       <c r="C2" t="str">
-        <v>Administrador</v>
+        <v>achinti morales hernández</v>
       </c>
       <c r="D2" t="str">
         <v>Sin cliente</v>
@@ -439,7 +439,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>65000</v>
+        <v>76000</v>
       </c>
       <c r="G2" t="str">
         <v>entregado</v>
@@ -447,13 +447,13 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-06-12 06:36:20</v>
+        <v>2026-06-16 20:39:20</v>
       </c>
       <c r="C3" t="str">
-        <v>Administrador</v>
+        <v>achinti morales hernández</v>
       </c>
       <c r="D3" t="str">
         <v>Sin cliente</v>
@@ -470,22 +470,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-06-12 06:31:22</v>
+        <v>2026-06-16 16:32:55</v>
       </c>
       <c r="C4" t="str">
-        <v>Administrador</v>
+        <v>achinti morales hernández</v>
       </c>
       <c r="D4" t="str">
-        <v>Sin cliente</v>
+        <v>javier</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="F4">
-        <v>76000</v>
+        <v>20000</v>
       </c>
       <c r="G4" t="str">
         <v>entregado</v>
@@ -493,13 +493,13 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-06-11 21:07:36</v>
+        <v>2026-06-16 16:22:12</v>
       </c>
       <c r="C5" t="str">
-        <v>Administrador</v>
+        <v>achinti morales hernández</v>
       </c>
       <c r="D5" t="str">
         <v>Sin cliente</v>
@@ -508,7 +508,7 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>170000</v>
+        <v>211000</v>
       </c>
       <c r="G5" t="str">
         <v>entregado</v>
@@ -516,10 +516,10 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-06-11 17:30:45</v>
+        <v>2026-06-16 14:29:33</v>
       </c>
       <c r="C6" t="str">
         <v>achinti morales hernández</v>
@@ -531,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>455000</v>
+        <v>165000</v>
       </c>
       <c r="G6" t="str">
         <v>entregado</v>
@@ -539,22 +539,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-06-11 17:29:29</v>
+        <v>2026-06-16 06:31:39</v>
       </c>
       <c r="C7" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="D7" t="str">
-        <v>Sin cliente</v>
+        <v>javier</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="F7">
-        <v>55000</v>
+        <v>38000</v>
       </c>
       <c r="G7" t="str">
         <v>entregado</v>
@@ -562,10 +562,10 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-06-11 17:07:24</v>
+        <v>2026-06-16 06:30:06</v>
       </c>
       <c r="C8" t="str">
         <v>achinti morales hernández</v>
@@ -577,7 +577,7 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>55000</v>
+        <v>76000</v>
       </c>
       <c r="G8" t="str">
         <v>entregado</v>
@@ -585,13 +585,13 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-06-11 16:55:29</v>
+        <v>2026-06-13 20:18:04</v>
       </c>
       <c r="C9" t="str">
-        <v>achinti morales hernández</v>
+        <v>Administrador</v>
       </c>
       <c r="D9" t="str">
         <v>Sin cliente</v>
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>55000</v>
+        <v>65000</v>
       </c>
       <c r="G9" t="str">
         <v>entregado</v>
@@ -608,13 +608,13 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-06-11 16:48:17</v>
+        <v>2026-06-12 06:36:20</v>
       </c>
       <c r="C10" t="str">
-        <v>achinti morales hernández</v>
+        <v>Administrador</v>
       </c>
       <c r="D10" t="str">
         <v>Sin cliente</v>
@@ -623,7 +623,7 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>55000</v>
+        <v>76000</v>
       </c>
       <c r="G10" t="str">
         <v>entregado</v>
@@ -631,13 +631,13 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-06-11 16:41:14</v>
+        <v>2026-06-12 06:31:22</v>
       </c>
       <c r="C11" t="str">
-        <v>achinti morales hernández</v>
+        <v>Administrador</v>
       </c>
       <c r="D11" t="str">
         <v>Sin cliente</v>
@@ -646,7 +646,7 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>55000</v>
+        <v>76000</v>
       </c>
       <c r="G11" t="str">
         <v>entregado</v>
@@ -654,13 +654,13 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-06-11 16:38:26</v>
+        <v>2026-06-11 21:07:36</v>
       </c>
       <c r="C12" t="str">
-        <v>achinti morales hernández</v>
+        <v>Administrador</v>
       </c>
       <c r="D12" t="str">
         <v>Sin cliente</v>
@@ -669,7 +669,7 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>55000</v>
+        <v>170000</v>
       </c>
       <c r="G12" t="str">
         <v>entregado</v>
@@ -677,10 +677,10 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-06-11 16:37:14</v>
+        <v>2026-06-11 17:30:45</v>
       </c>
       <c r="C13" t="str">
         <v>achinti morales hernández</v>
@@ -692,7 +692,7 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>55000</v>
+        <v>455000</v>
       </c>
       <c r="G13" t="str">
         <v>entregado</v>
@@ -700,10 +700,10 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-06-11 16:34:41</v>
+        <v>2026-06-11 17:29:29</v>
       </c>
       <c r="C14" t="str">
         <v>achinti morales hernández</v>
@@ -723,10 +723,10 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-06-11 16:32:51</v>
+        <v>2026-06-11 17:07:24</v>
       </c>
       <c r="C15" t="str">
         <v>achinti morales hernández</v>
@@ -746,10 +746,10 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-06-11 16:32:47</v>
+        <v>2026-06-11 16:55:29</v>
       </c>
       <c r="C16" t="str">
         <v>achinti morales hernández</v>
@@ -769,10 +769,10 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-06-11 09:19:13</v>
+        <v>2026-06-11 16:48:17</v>
       </c>
       <c r="C17" t="str">
         <v>achinti morales hernández</v>
@@ -784,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>120000</v>
+        <v>55000</v>
       </c>
       <c r="G17" t="str">
         <v>entregado</v>
@@ -792,10 +792,10 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-06-11 09:18:49</v>
+        <v>2026-06-11 16:41:14</v>
       </c>
       <c r="C18" t="str">
         <v>achinti morales hernández</v>
@@ -807,7 +807,7 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>120000</v>
+        <v>55000</v>
       </c>
       <c r="G18" t="str">
         <v>entregado</v>
@@ -815,10 +815,10 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-06-11 09:18:25</v>
+        <v>2026-06-11 16:38:26</v>
       </c>
       <c r="C19" t="str">
         <v>achinti morales hernández</v>
@@ -830,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>720000</v>
+        <v>55000</v>
       </c>
       <c r="G19" t="str">
         <v>entregado</v>
@@ -838,10 +838,10 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-06-11 09:18:02</v>
+        <v>2026-06-11 16:37:14</v>
       </c>
       <c r="C20" t="str">
         <v>achinti morales hernández</v>
@@ -853,7 +853,7 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>4800000</v>
+        <v>55000</v>
       </c>
       <c r="G20" t="str">
         <v>entregado</v>
@@ -861,10 +861,10 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B21" t="str">
-        <v>2026-06-11 09:16:29</v>
+        <v>2026-06-11 16:34:41</v>
       </c>
       <c r="C21" t="str">
         <v>achinti morales hernández</v>
@@ -876,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>560000</v>
+        <v>55000</v>
       </c>
       <c r="G21" t="str">
         <v>entregado</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B22" t="str">
-        <v>2026-06-11 09:12:56</v>
+        <v>2026-06-11 16:32:51</v>
       </c>
       <c r="C22" t="str">
         <v>achinti morales hernández</v>
@@ -899,7 +899,7 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>120000</v>
+        <v>55000</v>
       </c>
       <c r="G22" t="str">
         <v>entregado</v>
@@ -907,13 +907,13 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B23" t="str">
-        <v>2026-06-11 09:10:01</v>
+        <v>2026-06-11 16:32:47</v>
       </c>
       <c r="C23" t="str">
-        <v>Administrador</v>
+        <v>achinti morales hernández</v>
       </c>
       <c r="D23" t="str">
         <v>Sin cliente</v>
@@ -922,7 +922,7 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>105000</v>
+        <v>55000</v>
       </c>
       <c r="G23" t="str">
         <v>entregado</v>
@@ -930,13 +930,13 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B24" t="str">
-        <v>2026-06-11 09:08:21</v>
+        <v>2026-06-11 09:19:13</v>
       </c>
       <c r="C24" t="str">
-        <v>Administrador</v>
+        <v>achinti morales hernández</v>
       </c>
       <c r="D24" t="str">
         <v>Sin cliente</v>
@@ -945,7 +945,7 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>105000</v>
+        <v>120000</v>
       </c>
       <c r="G24" t="str">
         <v>entregado</v>
@@ -953,13 +953,13 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B25" t="str">
-        <v>2026-06-11 07:36:14</v>
+        <v>2026-06-11 09:18:49</v>
       </c>
       <c r="C25" t="str">
-        <v>Administrador</v>
+        <v>achinti morales hernández</v>
       </c>
       <c r="D25" t="str">
         <v>Sin cliente</v>
@@ -968,7 +968,7 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>105000</v>
+        <v>120000</v>
       </c>
       <c r="G25" t="str">
         <v>entregado</v>
@@ -976,30 +976,191 @@
     </row>
     <row r="26">
       <c r="A26">
+        <v>8</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2026-06-11 09:18:25</v>
+      </c>
+      <c r="C26" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Sin cliente</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>720000</v>
+      </c>
+      <c r="G26" t="str">
+        <v>entregado</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>7</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2026-06-11 09:18:02</v>
+      </c>
+      <c r="C27" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Sin cliente</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>4800000</v>
+      </c>
+      <c r="G27" t="str">
+        <v>entregado</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>6</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2026-06-11 09:16:29</v>
+      </c>
+      <c r="C28" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Sin cliente</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>560000</v>
+      </c>
+      <c r="G28" t="str">
+        <v>entregado</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>5</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2026-06-11 09:12:56</v>
+      </c>
+      <c r="C29" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Sin cliente</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>120000</v>
+      </c>
+      <c r="G29" t="str">
+        <v>entregado</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2026-06-11 09:10:01</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Administrador</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Sin cliente</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>105000</v>
+      </c>
+      <c r="G30" t="str">
+        <v>entregado</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>3</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2026-06-11 09:08:21</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Administrador</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Sin cliente</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>105000</v>
+      </c>
+      <c r="G31" t="str">
+        <v>entregado</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>2</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2026-06-11 07:36:14</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Administrador</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Sin cliente</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>105000</v>
+      </c>
+      <c r="G32" t="str">
+        <v>entregado</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
         <v>1</v>
       </c>
-      <c r="B26" t="str">
+      <c r="B33" t="str">
         <v>2026-06-11 07:16:23</v>
       </c>
-      <c r="C26" t="str">
+      <c r="C33" t="str">
         <v>Administrador</v>
       </c>
-      <c r="D26" t="str">
-        <v>Sin cliente</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
+      <c r="D33" t="str">
+        <v>Sin cliente</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
         <v>105000</v>
       </c>
-      <c r="G26" t="str">
+      <c r="G33" t="str">
         <v>entregado</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G33"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reportes/ventas.xlsx
+++ b/reportes/ventas.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:H50"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,15 +419,18 @@
         <v>Total cobrado</v>
       </c>
       <c r="G1" t="str">
+        <v>Metodo pago</v>
+      </c>
+      <c r="H1" t="str">
         <v>Estado</v>
       </c>
     </row>
     <row r="2">
       <c r="A2">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-16 20:39:32</v>
+        <v>2026-06-25 07:19:13</v>
       </c>
       <c r="C2" t="str">
         <v>achinti morales hernández</v>
@@ -442,15 +445,18 @@
         <v>76000</v>
       </c>
       <c r="G2" t="str">
+        <v>transferencia</v>
+      </c>
+      <c r="H2" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-06-16 20:39:20</v>
+        <v>2026-06-22 14:23:24</v>
       </c>
       <c r="C3" t="str">
         <v>achinti morales hernández</v>
@@ -462,41 +468,47 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>76000</v>
+        <v>101000</v>
       </c>
       <c r="G3" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H3" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-06-16 16:32:55</v>
+        <v>2026-06-22 14:21:42</v>
       </c>
       <c r="C4" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="D4" t="str">
-        <v>javier</v>
+        <v>Sin cliente</v>
       </c>
       <c r="E4">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>20000</v>
+        <v>101000</v>
       </c>
       <c r="G4" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H4" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-06-16 16:22:12</v>
+        <v>2026-06-22 14:06:11</v>
       </c>
       <c r="C5" t="str">
         <v>achinti morales hernández</v>
@@ -508,18 +520,21 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>211000</v>
+        <v>101000</v>
       </c>
       <c r="G5" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H5" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-06-16 14:29:33</v>
+        <v>2026-06-22 14:05:17</v>
       </c>
       <c r="C6" t="str">
         <v>achinti morales hernández</v>
@@ -531,67 +546,76 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>165000</v>
+        <v>101000</v>
       </c>
       <c r="G6" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H6" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-06-16 06:31:39</v>
+        <v>2026-06-22 06:48:49</v>
       </c>
       <c r="C7" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="D7" t="str">
-        <v>javier</v>
+        <v>Sin cliente</v>
       </c>
       <c r="E7">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>38000</v>
+        <v>585000</v>
       </c>
       <c r="G7" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H7" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-06-16 06:30:06</v>
+        <v>2026-06-19 15:37:06</v>
       </c>
       <c r="C8" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="D8" t="str">
-        <v>Sin cliente</v>
+        <v>achinti m</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>51500</v>
       </c>
       <c r="F8">
-        <v>76000</v>
+        <v>51500</v>
       </c>
       <c r="G8" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H8" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-06-13 20:18:04</v>
+        <v>2026-06-19 15:27:08</v>
       </c>
       <c r="C9" t="str">
-        <v>Administrador</v>
+        <v>achinti morales hernández</v>
       </c>
       <c r="D9" t="str">
         <v>Sin cliente</v>
@@ -600,21 +624,24 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>65000</v>
+        <v>76000</v>
       </c>
       <c r="G9" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H9" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-06-12 06:36:20</v>
+        <v>2026-06-19 15:26:39</v>
       </c>
       <c r="C10" t="str">
-        <v>Administrador</v>
+        <v>achinti morales hernández</v>
       </c>
       <c r="D10" t="str">
         <v>Sin cliente</v>
@@ -626,18 +653,21 @@
         <v>76000</v>
       </c>
       <c r="G10" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H10" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-06-12 06:31:22</v>
+        <v>2026-06-19 14:38:28</v>
       </c>
       <c r="C11" t="str">
-        <v>Administrador</v>
+        <v>achinti morales hernández</v>
       </c>
       <c r="D11" t="str">
         <v>Sin cliente</v>
@@ -646,21 +676,24 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>76000</v>
+        <v>65000</v>
       </c>
       <c r="G11" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H11" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-06-11 21:07:36</v>
+        <v>2026-06-19 14:34:54</v>
       </c>
       <c r="C12" t="str">
-        <v>Administrador</v>
+        <v>achinti morales hernández</v>
       </c>
       <c r="D12" t="str">
         <v>Sin cliente</v>
@@ -669,18 +702,21 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>170000</v>
+        <v>76000</v>
       </c>
       <c r="G12" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H12" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-06-11 17:30:45</v>
+        <v>2026-06-19 14:33:26</v>
       </c>
       <c r="C13" t="str">
         <v>achinti morales hernández</v>
@@ -692,41 +728,47 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>455000</v>
+        <v>76000</v>
       </c>
       <c r="G13" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H13" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-06-11 17:29:29</v>
+        <v>2026-06-19 14:32:46</v>
       </c>
       <c r="C14" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="D14" t="str">
-        <v>Sin cliente</v>
+        <v>achinti</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="F14">
-        <v>55000</v>
+        <v>38000</v>
       </c>
       <c r="G14" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H14" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-06-11 17:07:24</v>
+        <v>2026-06-19 14:31:23</v>
       </c>
       <c r="C15" t="str">
         <v>achinti morales hernández</v>
@@ -738,18 +780,21 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>55000</v>
+        <v>76000</v>
       </c>
       <c r="G15" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H15" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-06-11 16:55:29</v>
+        <v>2026-06-19 14:27:50</v>
       </c>
       <c r="C16" t="str">
         <v>achinti morales hernández</v>
@@ -761,18 +806,21 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>55000</v>
+        <v>76000</v>
       </c>
       <c r="G16" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H16" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-06-11 16:48:17</v>
+        <v>2026-06-19 14:11:30</v>
       </c>
       <c r="C17" t="str">
         <v>achinti morales hernández</v>
@@ -784,18 +832,21 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>55000</v>
+        <v>76000</v>
       </c>
       <c r="G17" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H17" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-06-11 16:41:14</v>
+        <v>2026-06-19 14:08:49</v>
       </c>
       <c r="C18" t="str">
         <v>achinti morales hernández</v>
@@ -807,18 +858,21 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>55000</v>
+        <v>76000</v>
       </c>
       <c r="G18" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H18" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-06-11 16:38:26</v>
+        <v>2026-06-16 20:39:32</v>
       </c>
       <c r="C19" t="str">
         <v>achinti morales hernández</v>
@@ -830,18 +884,21 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>55000</v>
+        <v>76000</v>
       </c>
       <c r="G19" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H19" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-06-11 16:37:14</v>
+        <v>2026-06-16 20:39:20</v>
       </c>
       <c r="C20" t="str">
         <v>achinti morales hernández</v>
@@ -853,41 +910,47 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>55000</v>
+        <v>76000</v>
       </c>
       <c r="G20" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H20" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="B21" t="str">
-        <v>2026-06-11 16:34:41</v>
+        <v>2026-06-16 16:32:55</v>
       </c>
       <c r="C21" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="D21" t="str">
-        <v>Sin cliente</v>
+        <v>javier</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="F21">
-        <v>55000</v>
+        <v>20000</v>
       </c>
       <c r="G21" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H21" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B22" t="str">
-        <v>2026-06-11 16:32:51</v>
+        <v>2026-06-16 16:22:12</v>
       </c>
       <c r="C22" t="str">
         <v>achinti morales hernández</v>
@@ -899,18 +962,21 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>55000</v>
+        <v>211000</v>
       </c>
       <c r="G22" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H22" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="B23" t="str">
-        <v>2026-06-11 16:32:47</v>
+        <v>2026-06-16 14:29:33</v>
       </c>
       <c r="C23" t="str">
         <v>achinti morales hernández</v>
@@ -922,41 +988,47 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>55000</v>
+        <v>165000</v>
       </c>
       <c r="G23" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H23" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="B24" t="str">
-        <v>2026-06-11 09:19:13</v>
+        <v>2026-06-16 06:31:39</v>
       </c>
       <c r="C24" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="D24" t="str">
-        <v>Sin cliente</v>
+        <v>javier</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="F24">
-        <v>120000</v>
+        <v>38000</v>
       </c>
       <c r="G24" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H24" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="B25" t="str">
-        <v>2026-06-11 09:18:49</v>
+        <v>2026-06-16 06:30:06</v>
       </c>
       <c r="C25" t="str">
         <v>achinti morales hernández</v>
@@ -968,21 +1040,24 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>120000</v>
+        <v>76000</v>
       </c>
       <c r="G25" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H25" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>2026-06-11 09:18:25</v>
+        <v>2026-06-13 20:18:04</v>
       </c>
       <c r="C26" t="str">
-        <v>achinti morales hernández</v>
+        <v>Administrador</v>
       </c>
       <c r="D26" t="str">
         <v>Sin cliente</v>
@@ -991,21 +1066,24 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>720000</v>
+        <v>65000</v>
       </c>
       <c r="G26" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H26" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B27" t="str">
-        <v>2026-06-11 09:18:02</v>
+        <v>2026-06-12 06:36:20</v>
       </c>
       <c r="C27" t="str">
-        <v>achinti morales hernández</v>
+        <v>Administrador</v>
       </c>
       <c r="D27" t="str">
         <v>Sin cliente</v>
@@ -1014,21 +1092,24 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>4800000</v>
+        <v>76000</v>
       </c>
       <c r="G27" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H27" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B28" t="str">
-        <v>2026-06-11 09:16:29</v>
+        <v>2026-06-12 06:31:22</v>
       </c>
       <c r="C28" t="str">
-        <v>achinti morales hernández</v>
+        <v>Administrador</v>
       </c>
       <c r="D28" t="str">
         <v>Sin cliente</v>
@@ -1037,21 +1118,24 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>560000</v>
+        <v>76000</v>
       </c>
       <c r="G28" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H28" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B29" t="str">
-        <v>2026-06-11 09:12:56</v>
+        <v>2026-06-11 21:07:36</v>
       </c>
       <c r="C29" t="str">
-        <v>achinti morales hernández</v>
+        <v>Administrador</v>
       </c>
       <c r="D29" t="str">
         <v>Sin cliente</v>
@@ -1060,21 +1144,24 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>120000</v>
+        <v>170000</v>
       </c>
       <c r="G29" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H29" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-06-11 09:10:01</v>
+        <v>2026-06-11 17:30:45</v>
       </c>
       <c r="C30" t="str">
-        <v>Administrador</v>
+        <v>achinti morales hernández</v>
       </c>
       <c r="D30" t="str">
         <v>Sin cliente</v>
@@ -1083,21 +1170,24 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>105000</v>
+        <v>455000</v>
       </c>
       <c r="G30" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H30" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B31" t="str">
-        <v>2026-06-11 09:08:21</v>
+        <v>2026-06-11 17:29:29</v>
       </c>
       <c r="C31" t="str">
-        <v>Administrador</v>
+        <v>achinti morales hernández</v>
       </c>
       <c r="D31" t="str">
         <v>Sin cliente</v>
@@ -1106,21 +1196,24 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>105000</v>
+        <v>55000</v>
       </c>
       <c r="G31" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H31" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B32" t="str">
-        <v>2026-06-11 07:36:14</v>
+        <v>2026-06-11 17:07:24</v>
       </c>
       <c r="C32" t="str">
-        <v>Administrador</v>
+        <v>achinti morales hernández</v>
       </c>
       <c r="D32" t="str">
         <v>Sin cliente</v>
@@ -1129,38 +1222,486 @@
         <v>0</v>
       </c>
       <c r="F32">
-        <v>105000</v>
+        <v>55000</v>
       </c>
       <c r="G32" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H32" t="str">
         <v>entregado</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
+        <v>18</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2026-06-11 16:55:29</v>
+      </c>
+      <c r="C33" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Sin cliente</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>55000</v>
+      </c>
+      <c r="G33" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H33" t="str">
+        <v>entregado</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>17</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2026-06-11 16:48:17</v>
+      </c>
+      <c r="C34" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Sin cliente</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>55000</v>
+      </c>
+      <c r="G34" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H34" t="str">
+        <v>entregado</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>16</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2026-06-11 16:41:14</v>
+      </c>
+      <c r="C35" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Sin cliente</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>55000</v>
+      </c>
+      <c r="G35" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H35" t="str">
+        <v>entregado</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>15</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2026-06-11 16:38:26</v>
+      </c>
+      <c r="C36" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Sin cliente</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>55000</v>
+      </c>
+      <c r="G36" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H36" t="str">
+        <v>entregado</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>14</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2026-06-11 16:37:14</v>
+      </c>
+      <c r="C37" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Sin cliente</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>55000</v>
+      </c>
+      <c r="G37" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H37" t="str">
+        <v>entregado</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>13</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2026-06-11 16:34:41</v>
+      </c>
+      <c r="C38" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Sin cliente</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>55000</v>
+      </c>
+      <c r="G38" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H38" t="str">
+        <v>entregado</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>12</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2026-06-11 16:32:51</v>
+      </c>
+      <c r="C39" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Sin cliente</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>55000</v>
+      </c>
+      <c r="G39" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H39" t="str">
+        <v>entregado</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>11</v>
+      </c>
+      <c r="B40" t="str">
+        <v>2026-06-11 16:32:47</v>
+      </c>
+      <c r="C40" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Sin cliente</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>55000</v>
+      </c>
+      <c r="G40" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H40" t="str">
+        <v>entregado</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>10</v>
+      </c>
+      <c r="B41" t="str">
+        <v>2026-06-11 09:19:13</v>
+      </c>
+      <c r="C41" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Sin cliente</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>120000</v>
+      </c>
+      <c r="G41" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H41" t="str">
+        <v>entregado</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>9</v>
+      </c>
+      <c r="B42" t="str">
+        <v>2026-06-11 09:18:49</v>
+      </c>
+      <c r="C42" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Sin cliente</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>120000</v>
+      </c>
+      <c r="G42" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H42" t="str">
+        <v>entregado</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>8</v>
+      </c>
+      <c r="B43" t="str">
+        <v>2026-06-11 09:18:25</v>
+      </c>
+      <c r="C43" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Sin cliente</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>720000</v>
+      </c>
+      <c r="G43" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H43" t="str">
+        <v>entregado</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>7</v>
+      </c>
+      <c r="B44" t="str">
+        <v>2026-06-11 09:18:02</v>
+      </c>
+      <c r="C44" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Sin cliente</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>4800000</v>
+      </c>
+      <c r="G44" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H44" t="str">
+        <v>entregado</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>6</v>
+      </c>
+      <c r="B45" t="str">
+        <v>2026-06-11 09:16:29</v>
+      </c>
+      <c r="C45" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Sin cliente</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>560000</v>
+      </c>
+      <c r="G45" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H45" t="str">
+        <v>entregado</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>5</v>
+      </c>
+      <c r="B46" t="str">
+        <v>2026-06-11 09:12:56</v>
+      </c>
+      <c r="C46" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Sin cliente</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>120000</v>
+      </c>
+      <c r="G46" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H46" t="str">
+        <v>entregado</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>4</v>
+      </c>
+      <c r="B47" t="str">
+        <v>2026-06-11 09:10:01</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Administrador</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Sin cliente</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>105000</v>
+      </c>
+      <c r="G47" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H47" t="str">
+        <v>entregado</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>3</v>
+      </c>
+      <c r="B48" t="str">
+        <v>2026-06-11 09:08:21</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Administrador</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Sin cliente</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>105000</v>
+      </c>
+      <c r="G48" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H48" t="str">
+        <v>entregado</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>2</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2026-06-11 07:36:14</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Administrador</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Sin cliente</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>105000</v>
+      </c>
+      <c r="G49" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H49" t="str">
+        <v>entregado</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
         <v>1</v>
       </c>
-      <c r="B33" t="str">
+      <c r="B50" t="str">
         <v>2026-06-11 07:16:23</v>
       </c>
-      <c r="C33" t="str">
+      <c r="C50" t="str">
         <v>Administrador</v>
       </c>
-      <c r="D33" t="str">
-        <v>Sin cliente</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-      <c r="F33">
+      <c r="D50" t="str">
+        <v>Sin cliente</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
         <v>105000</v>
       </c>
-      <c r="G33" t="str">
+      <c r="G50" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H50" t="str">
         <v>entregado</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G33"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H50"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reportes/ventas.xlsx
+++ b/reportes/ventas.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,10 +427,10 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-25 07:19:13</v>
+        <v>2026-06-25 15:29:41</v>
       </c>
       <c r="C2" t="str">
         <v>achinti morales hernández</v>
@@ -453,10 +453,10 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-06-22 14:23:24</v>
+        <v>2026-06-25 07:19:13</v>
       </c>
       <c r="C3" t="str">
         <v>achinti morales hernández</v>
@@ -468,10 +468,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>101000</v>
+        <v>76000</v>
       </c>
       <c r="G3" t="str">
-        <v>efectivo</v>
+        <v>transferencia</v>
       </c>
       <c r="H3" t="str">
         <v>entregado</v>
@@ -479,10 +479,10 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-06-22 14:21:42</v>
+        <v>2026-06-22 14:23:24</v>
       </c>
       <c r="C4" t="str">
         <v>achinti morales hernández</v>
@@ -505,10 +505,10 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-06-22 14:06:11</v>
+        <v>2026-06-22 14:21:42</v>
       </c>
       <c r="C5" t="str">
         <v>achinti morales hernández</v>
@@ -531,10 +531,10 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-06-22 14:05:17</v>
+        <v>2026-06-22 14:06:11</v>
       </c>
       <c r="C6" t="str">
         <v>achinti morales hernández</v>
@@ -557,10 +557,10 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-06-22 06:48:49</v>
+        <v>2026-06-22 14:05:17</v>
       </c>
       <c r="C7" t="str">
         <v>achinti morales hernández</v>
@@ -572,7 +572,7 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>585000</v>
+        <v>101000</v>
       </c>
       <c r="G7" t="str">
         <v>efectivo</v>
@@ -583,22 +583,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-06-19 15:37:06</v>
+        <v>2026-06-22 06:48:49</v>
       </c>
       <c r="C8" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="D8" t="str">
-        <v>achinti m</v>
+        <v>Sin cliente</v>
       </c>
       <c r="E8">
-        <v>51500</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>51500</v>
+        <v>585000</v>
       </c>
       <c r="G8" t="str">
         <v>efectivo</v>
@@ -609,22 +609,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-06-19 15:27:08</v>
+        <v>2026-06-19 15:37:06</v>
       </c>
       <c r="C9" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="D9" t="str">
-        <v>Sin cliente</v>
+        <v>achinti m</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>51500</v>
       </c>
       <c r="F9">
-        <v>76000</v>
+        <v>51500</v>
       </c>
       <c r="G9" t="str">
         <v>efectivo</v>
@@ -635,10 +635,10 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-06-19 15:26:39</v>
+        <v>2026-06-19 15:27:08</v>
       </c>
       <c r="C10" t="str">
         <v>achinti morales hernández</v>
@@ -661,10 +661,10 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-06-19 14:38:28</v>
+        <v>2026-06-19 15:26:39</v>
       </c>
       <c r="C11" t="str">
         <v>achinti morales hernández</v>
@@ -676,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>65000</v>
+        <v>76000</v>
       </c>
       <c r="G11" t="str">
         <v>efectivo</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-06-19 14:34:54</v>
+        <v>2026-06-19 14:38:28</v>
       </c>
       <c r="C12" t="str">
         <v>achinti morales hernández</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>76000</v>
+        <v>65000</v>
       </c>
       <c r="G12" t="str">
         <v>efectivo</v>
@@ -713,10 +713,10 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-06-19 14:33:26</v>
+        <v>2026-06-19 14:34:54</v>
       </c>
       <c r="C13" t="str">
         <v>achinti morales hernández</v>
@@ -739,22 +739,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-06-19 14:32:46</v>
+        <v>2026-06-19 14:33:26</v>
       </c>
       <c r="C14" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="D14" t="str">
-        <v>achinti</v>
+        <v>Sin cliente</v>
       </c>
       <c r="E14">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>38000</v>
+        <v>76000</v>
       </c>
       <c r="G14" t="str">
         <v>efectivo</v>
@@ -765,22 +765,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-06-19 14:31:23</v>
+        <v>2026-06-19 14:32:46</v>
       </c>
       <c r="C15" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="D15" t="str">
-        <v>Sin cliente</v>
+        <v>achinti</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="F15">
-        <v>76000</v>
+        <v>38000</v>
       </c>
       <c r="G15" t="str">
         <v>efectivo</v>
@@ -791,10 +791,10 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-06-19 14:27:50</v>
+        <v>2026-06-19 14:31:23</v>
       </c>
       <c r="C16" t="str">
         <v>achinti morales hernández</v>
@@ -817,10 +817,10 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-06-19 14:11:30</v>
+        <v>2026-06-19 14:27:50</v>
       </c>
       <c r="C17" t="str">
         <v>achinti morales hernández</v>
@@ -843,10 +843,10 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-06-19 14:08:49</v>
+        <v>2026-06-19 14:11:30</v>
       </c>
       <c r="C18" t="str">
         <v>achinti morales hernández</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-06-16 20:39:32</v>
+        <v>2026-06-19 14:08:49</v>
       </c>
       <c r="C19" t="str">
         <v>achinti morales hernández</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-06-16 20:39:20</v>
+        <v>2026-06-16 20:39:32</v>
       </c>
       <c r="C20" t="str">
         <v>achinti morales hernández</v>
@@ -921,22 +921,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21" t="str">
-        <v>2026-06-16 16:32:55</v>
+        <v>2026-06-16 20:39:20</v>
       </c>
       <c r="C21" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="D21" t="str">
-        <v>javier</v>
+        <v>Sin cliente</v>
       </c>
       <c r="E21">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>20000</v>
+        <v>76000</v>
       </c>
       <c r="G21" t="str">
         <v>efectivo</v>
@@ -947,22 +947,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" t="str">
-        <v>2026-06-16 16:22:12</v>
+        <v>2026-06-16 16:32:55</v>
       </c>
       <c r="C22" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="D22" t="str">
-        <v>Sin cliente</v>
+        <v>javier</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="F22">
-        <v>211000</v>
+        <v>20000</v>
       </c>
       <c r="G22" t="str">
         <v>efectivo</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B23" t="str">
-        <v>2026-06-16 14:29:33</v>
+        <v>2026-06-16 16:22:12</v>
       </c>
       <c r="C23" t="str">
         <v>achinti morales hernández</v>
@@ -988,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>165000</v>
+        <v>211000</v>
       </c>
       <c r="G23" t="str">
         <v>efectivo</v>
@@ -999,22 +999,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B24" t="str">
-        <v>2026-06-16 06:31:39</v>
+        <v>2026-06-16 14:29:33</v>
       </c>
       <c r="C24" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="D24" t="str">
-        <v>javier</v>
+        <v>Sin cliente</v>
       </c>
       <c r="E24">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>38000</v>
+        <v>165000</v>
       </c>
       <c r="G24" t="str">
         <v>efectivo</v>
@@ -1025,22 +1025,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B25" t="str">
-        <v>2026-06-16 06:30:06</v>
+        <v>2026-06-16 06:31:39</v>
       </c>
       <c r="C25" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="D25" t="str">
-        <v>Sin cliente</v>
+        <v>javier</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="F25">
-        <v>76000</v>
+        <v>38000</v>
       </c>
       <c r="G25" t="str">
         <v>efectivo</v>
@@ -1051,13 +1051,13 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" t="str">
-        <v>2026-06-13 20:18:04</v>
+        <v>2026-06-16 06:30:06</v>
       </c>
       <c r="C26" t="str">
-        <v>Administrador</v>
+        <v>achinti morales hernández</v>
       </c>
       <c r="D26" t="str">
         <v>Sin cliente</v>
@@ -1066,7 +1066,7 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>65000</v>
+        <v>76000</v>
       </c>
       <c r="G26" t="str">
         <v>efectivo</v>
@@ -1077,10 +1077,10 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B27" t="str">
-        <v>2026-06-12 06:36:20</v>
+        <v>2026-06-13 20:18:04</v>
       </c>
       <c r="C27" t="str">
         <v>Administrador</v>
@@ -1092,7 +1092,7 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>76000</v>
+        <v>65000</v>
       </c>
       <c r="G27" t="str">
         <v>efectivo</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B28" t="str">
-        <v>2026-06-12 06:31:22</v>
+        <v>2026-06-12 06:36:20</v>
       </c>
       <c r="C28" t="str">
         <v>Administrador</v>
@@ -1129,10 +1129,10 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B29" t="str">
-        <v>2026-06-11 21:07:36</v>
+        <v>2026-06-12 06:31:22</v>
       </c>
       <c r="C29" t="str">
         <v>Administrador</v>
@@ -1144,7 +1144,7 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>170000</v>
+        <v>76000</v>
       </c>
       <c r="G29" t="str">
         <v>efectivo</v>
@@ -1155,13 +1155,13 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-06-11 17:30:45</v>
+        <v>2026-06-11 21:07:36</v>
       </c>
       <c r="C30" t="str">
-        <v>achinti morales hernández</v>
+        <v>Administrador</v>
       </c>
       <c r="D30" t="str">
         <v>Sin cliente</v>
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>455000</v>
+        <v>170000</v>
       </c>
       <c r="G30" t="str">
         <v>efectivo</v>
@@ -1181,10 +1181,10 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B31" t="str">
-        <v>2026-06-11 17:29:29</v>
+        <v>2026-06-11 17:30:45</v>
       </c>
       <c r="C31" t="str">
         <v>achinti morales hernández</v>
@@ -1196,7 +1196,7 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>55000</v>
+        <v>455000</v>
       </c>
       <c r="G31" t="str">
         <v>efectivo</v>
@@ -1207,10 +1207,10 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B32" t="str">
-        <v>2026-06-11 17:07:24</v>
+        <v>2026-06-11 17:29:29</v>
       </c>
       <c r="C32" t="str">
         <v>achinti morales hernández</v>
@@ -1233,10 +1233,10 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B33" t="str">
-        <v>2026-06-11 16:55:29</v>
+        <v>2026-06-11 17:07:24</v>
       </c>
       <c r="C33" t="str">
         <v>achinti morales hernández</v>
@@ -1259,10 +1259,10 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B34" t="str">
-        <v>2026-06-11 16:48:17</v>
+        <v>2026-06-11 16:55:29</v>
       </c>
       <c r="C34" t="str">
         <v>achinti morales hernández</v>
@@ -1285,10 +1285,10 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B35" t="str">
-        <v>2026-06-11 16:41:14</v>
+        <v>2026-06-11 16:48:17</v>
       </c>
       <c r="C35" t="str">
         <v>achinti morales hernández</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B36" t="str">
-        <v>2026-06-11 16:38:26</v>
+        <v>2026-06-11 16:41:14</v>
       </c>
       <c r="C36" t="str">
         <v>achinti morales hernández</v>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B37" t="str">
-        <v>2026-06-11 16:37:14</v>
+        <v>2026-06-11 16:38:26</v>
       </c>
       <c r="C37" t="str">
         <v>achinti morales hernández</v>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B38" t="str">
-        <v>2026-06-11 16:34:41</v>
+        <v>2026-06-11 16:37:14</v>
       </c>
       <c r="C38" t="str">
         <v>achinti morales hernández</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B39" t="str">
-        <v>2026-06-11 16:32:51</v>
+        <v>2026-06-11 16:34:41</v>
       </c>
       <c r="C39" t="str">
         <v>achinti morales hernández</v>
@@ -1415,10 +1415,10 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B40" t="str">
-        <v>2026-06-11 16:32:47</v>
+        <v>2026-06-11 16:32:51</v>
       </c>
       <c r="C40" t="str">
         <v>achinti morales hernández</v>
@@ -1441,10 +1441,10 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B41" t="str">
-        <v>2026-06-11 09:19:13</v>
+        <v>2026-06-11 16:32:47</v>
       </c>
       <c r="C41" t="str">
         <v>achinti morales hernández</v>
@@ -1456,7 +1456,7 @@
         <v>0</v>
       </c>
       <c r="F41">
-        <v>120000</v>
+        <v>55000</v>
       </c>
       <c r="G41" t="str">
         <v>efectivo</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B42" t="str">
-        <v>2026-06-11 09:18:49</v>
+        <v>2026-06-11 09:19:13</v>
       </c>
       <c r="C42" t="str">
         <v>achinti morales hernández</v>
@@ -1493,10 +1493,10 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B43" t="str">
-        <v>2026-06-11 09:18:25</v>
+        <v>2026-06-11 09:18:49</v>
       </c>
       <c r="C43" t="str">
         <v>achinti morales hernández</v>
@@ -1508,7 +1508,7 @@
         <v>0</v>
       </c>
       <c r="F43">
-        <v>720000</v>
+        <v>120000</v>
       </c>
       <c r="G43" t="str">
         <v>efectivo</v>
@@ -1519,10 +1519,10 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B44" t="str">
-        <v>2026-06-11 09:18:02</v>
+        <v>2026-06-11 09:18:25</v>
       </c>
       <c r="C44" t="str">
         <v>achinti morales hernández</v>
@@ -1534,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="F44">
-        <v>4800000</v>
+        <v>720000</v>
       </c>
       <c r="G44" t="str">
         <v>efectivo</v>
@@ -1545,10 +1545,10 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B45" t="str">
-        <v>2026-06-11 09:16:29</v>
+        <v>2026-06-11 09:18:02</v>
       </c>
       <c r="C45" t="str">
         <v>achinti morales hernández</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="F45">
-        <v>560000</v>
+        <v>4800000</v>
       </c>
       <c r="G45" t="str">
         <v>efectivo</v>
@@ -1571,10 +1571,10 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B46" t="str">
-        <v>2026-06-11 09:12:56</v>
+        <v>2026-06-11 09:16:29</v>
       </c>
       <c r="C46" t="str">
         <v>achinti morales hernández</v>
@@ -1586,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="F46">
-        <v>120000</v>
+        <v>560000</v>
       </c>
       <c r="G46" t="str">
         <v>efectivo</v>
@@ -1597,13 +1597,13 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B47" t="str">
-        <v>2026-06-11 09:10:01</v>
+        <v>2026-06-11 09:12:56</v>
       </c>
       <c r="C47" t="str">
-        <v>Administrador</v>
+        <v>achinti morales hernández</v>
       </c>
       <c r="D47" t="str">
         <v>Sin cliente</v>
@@ -1612,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="F47">
-        <v>105000</v>
+        <v>120000</v>
       </c>
       <c r="G47" t="str">
         <v>efectivo</v>
@@ -1623,10 +1623,10 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B48" t="str">
-        <v>2026-06-11 09:08:21</v>
+        <v>2026-06-11 09:10:01</v>
       </c>
       <c r="C48" t="str">
         <v>Administrador</v>
@@ -1649,10 +1649,10 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B49" t="str">
-        <v>2026-06-11 07:36:14</v>
+        <v>2026-06-11 09:08:21</v>
       </c>
       <c r="C49" t="str">
         <v>Administrador</v>
@@ -1675,10 +1675,10 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B50" t="str">
-        <v>2026-06-11 07:16:23</v>
+        <v>2026-06-11 07:36:14</v>
       </c>
       <c r="C50" t="str">
         <v>Administrador</v>
@@ -1699,9 +1699,35 @@
         <v>entregado</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51">
+        <v>1</v>
+      </c>
+      <c r="B51" t="str">
+        <v>2026-06-11 07:16:23</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Administrador</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Sin cliente</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>105000</v>
+      </c>
+      <c r="G51" t="str">
+        <v>efectivo</v>
+      </c>
+      <c r="H51" t="str">
+        <v>entregado</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H51"/>
   </ignoredErrors>
 </worksheet>
 </file>